--- a/server/tests/fixtures/lk-export-sample.xlsx
+++ b/server/tests/fixtures/lk-export-sample.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G2" s="1" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
@@ -548,7 +548,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G10" s="1" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
@@ -944,7 +944,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G21" s="1" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G22" s="1" t="n">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G23" s="1" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G24" s="1" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G25" s="1" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G30" s="1" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7701234567</t>
+          <t>7701234560</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
